--- a/data/trans_dic/P25C$otraforma_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25C$otraforma_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue otro</t>
+          <t>Población cuyo método para dejar de fumar fue otro (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,49</t>
+          <t>0,0; 27,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,95</t>
+          <t>0,0; 14,0</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,62</t>
+          <t>0,0; 19,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 12,37</t>
+          <t>1,34; 13,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 10,83</t>
+          <t>1,43; 10,01</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,97</t>
+          <t>0,0; 4,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,41</t>
+          <t>0,78; 5,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 4,35</t>
+          <t>0,16; 4,12</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,09; 10,96</t>
+          <t>3,03; 11,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 8,75</t>
+          <t>1,48; 9,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,14; 9,2</t>
+          <t>3,16; 9,18</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,61; 7,77</t>
+          <t>1,79; 7,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,72</t>
+          <t>0,0; 6,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,06</t>
+          <t>1,4; 6,32</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,38</t>
+          <t>0,0; 5,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,35</t>
+          <t>0,0; 14,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,88</t>
+          <t>0,46; 5,06</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,69</t>
+          <t>0,96; 4,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,69</t>
+          <t>1,57; 4,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,05</t>
+          <t>1,48; 4,18</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue otro</t>
+          <t>Población cuyo método para dejar de fumar fue otro (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3403</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2654</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3071</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5884</t>
+          <t>0; 5762</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1879</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7655</t>
+          <t>0; 7169</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 8824</t>
+          <t>0; 8780</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>710; 6456</t>
+          <t>702; 6950</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1438; 10528</t>
+          <t>1386; 9730</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 17270</t>
+          <t>0; 16673</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>672; 5580</t>
+          <t>678; 4945</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>549; 18877</t>
+          <t>699; 17909</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4848; 17191</t>
+          <t>4754; 17827</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1296; 7539</t>
+          <t>1275; 8297</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7633; 22351</t>
+          <t>7684; 22319</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2506; 12089</t>
+          <t>2777; 12115</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3052</t>
+          <t>0; 2936</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2898; 12183</t>
+          <t>2806; 12696</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5109</t>
+          <t>0; 5905</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2890</t>
+          <t>0; 2512</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>612; 6565</t>
+          <t>615; 6797</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>8461; 39834</t>
+          <t>8153; 40995</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5309; 15816</t>
+          <t>5282; 15108</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16853; 48026</t>
+          <t>17537; 49645</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$otraforma_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25C$otraforma_2023-Edad-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,89</t>
+          <t>0,0; 23,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,0</t>
+          <t>0,0; 10,61</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,52</t>
+          <t>0,0; 16,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 13,31</t>
+          <t>0,33; 11,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 10,01</t>
+          <t>0,93; 9,8</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,8</t>
+          <t>1,16; 9,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,68</t>
+          <t>0,74; 6,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 4,12</t>
+          <t>1,36; 7,09</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,03; 11,36</t>
+          <t>3,19; 11,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 9,63</t>
+          <t>1,48; 9,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 9,18</t>
+          <t>3,36; 8,93</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,79; 7,79</t>
+          <t>2,0; 7,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,46</t>
+          <t>0,0; 6,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,4; 6,32</t>
+          <t>1,78; 6,8</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,06</t>
+          <t>0,0; 4,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,21</t>
+          <t>0,0; 16,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 5,06</t>
+          <t>0,45; 4,41</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,83</t>
+          <t>2,73; 6,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,48</t>
+          <t>1,45; 4,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,18</t>
+          <t>2,66; 4,95</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1222</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5762</t>
+          <t>0; 5950</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7169</t>
+          <t>0; 6346</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4150</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 8780</t>
+          <t>0; 8307</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>702; 6950</t>
+          <t>186; 6665</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1386; 9730</t>
+          <t>980; 10369</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>7090</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 16673</t>
+          <t>1314; 11268</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>678; 4945</t>
+          <t>681; 5935</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>699; 17909</t>
+          <t>2795; 14587</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>10713</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13594</t>
+          <t>14715</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4754; 17827</t>
+          <t>5266; 18922</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1275; 8297</t>
+          <t>1396; 8490</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7684; 22319</t>
+          <t>8704; 23156</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>7299</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>610</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>7909</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2777; 12115</t>
+          <t>3436; 13350</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2936</t>
+          <t>0; 3050</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2806; 12696</t>
+          <t>3928; 14971</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>670</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2297</t>
+          <t>2507</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5905</t>
+          <t>0; 6371</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2512</t>
+          <t>0; 3163</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>615; 6797</t>
+          <t>671; 6543</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>24296</t>
+          <t>27705</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33763</t>
+          <t>37593</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>8153; 40995</t>
+          <t>18024; 40558</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5282; 15108</t>
+          <t>5310; 15779</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17537; 49645</t>
+          <t>27280; 50816</t>
         </is>
       </c>
     </row>
